--- a/data/excel/Autommerce_Partners_Qatar.xlsx
+++ b/data/excel/Autommerce_Partners_Qatar.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partners" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Partners'!$A$1:$D$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Partners'!$A$1:$D$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -464,61 +464,61 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Seamedia E-commerce Solutions</t>
+          <t>Webkul</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://seamediainc.com</t>
+          <t>https://webkul.com</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Commerce9</t>
+          <t>INFORISE</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>https://commerce9.io</t>
+          <t>https://inforiseit.com</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Zero&amp;One</t>
+          <t>Seamedia E-commerce Solutions</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://zeroandone.me</t>
+          <t>https://seamediainc.com</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -530,17 +530,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Calliweb</t>
+          <t>Commerce9</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>https://calliweb.fr</t>
+          <t>https://commerce9.io</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -552,17 +552,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Embitel</t>
+          <t>Zero&amp;One</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://embitel.com</t>
+          <t>https://zeroandone.me</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -574,12 +574,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Rowwad Advisory &amp; Business Solutions</t>
+          <t>Calliweb</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://rowwad.qa</t>
+          <t>https://calliweb.fr</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -596,34 +596,34 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Inditech Technologies</t>
+          <t>Embitel</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>https://inditechme.com</t>
+          <t>https://embitel.com</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Technaureus</t>
+          <t>Rowwad Advisory &amp; Business Solutions</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>https://technaureus.com</t>
+          <t>https://rowwad.qa</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -633,151 +633,151 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Five Systems Development</t>
+          <t>Inditech Technologies</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>https://fivesysdev.com</t>
+          <t>https://inditechme.com</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Automation &amp; Workflow Consulting Firms</t>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Motif Agency</t>
+          <t>Technaureus</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>https://motif.net</t>
+          <t>https://technaureus.com</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce CRO &amp; UX/UI Agencies</t>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Nobrand Agency</t>
+          <t>Five Systems Development</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>https://nobrandagency.com</t>
+          <t>https://fivesysdev.com</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Technology Consultants</t>
+          <t>Ecommerce Automation &amp; Workflow Consulting Firms</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>MaXab.ai</t>
+          <t>Motif Agency</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>https://maxab.ai</t>
+          <t>https://motif.net</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce CRO &amp; UX/UI Agencies</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Cosmic Ventures</t>
+          <t>Nobrand Agency</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>https://cosmic.ventures</t>
+          <t>https://nobrandagency.com</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce SEO Agencies &amp; Consultants</t>
+          <t>Fashion Ecommerce Technology Consultants</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>MAGDIO</t>
+          <t>MaXab.ai</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>https://magdio.com</t>
+          <t>https://maxab.ai</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce SEO Agencies &amp; Consultants</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Digital Links</t>
+          <t>Cosmic Ventures</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>https://digitallinkspro.qa</t>
+          <t>https://cosmic.ventures</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Halabyte Technologies</t>
+          <t>MAGDIO</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>https://halabyte.com</t>
+          <t>https://magdio.com</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce SEO Agencies &amp; Consultants</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -816,83 +816,83 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Creative Loft</t>
+          <t>Digital Links</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>https://creativeloft.qa</t>
+          <t>https://digitallinkspro.qa</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
+          <t>Ecommerce SEO Agencies &amp; Consultants</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Taqnia Studio Qatar</t>
+          <t>Halabyte Technologies</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>https://taqnia.qa</t>
+          <t>https://halabyte.com</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Sociata</t>
+          <t>Creative Loft</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>https://sociata.com</t>
+          <t>https://creativeloft.qa</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>MSYS</t>
+          <t>Taqnia Studio Qatar</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>https://msys.agency</t>
+          <t>https://taqnia.qa</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Automation &amp; Workflow Consulting Firms</t>
+          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -904,17 +904,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Aura Qatar</t>
+          <t>Sociata</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>https://auraqatar.com</t>
+          <t>https://sociata.com</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -926,78 +926,78 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>nopStation</t>
+          <t>MSYS</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>https://nop-station.com</t>
+          <t>https://msys.agency</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
+          <t>Ecommerce Automation &amp; Workflow Consulting Firms</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>NULogic</t>
+          <t>Aura Qatar</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>https://nulogic.io</t>
+          <t>https://auraqatar.com</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Personalization &amp; Customer Experience Agencies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>88medias</t>
+          <t>nopStation</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>https://88medias.com</t>
+          <t>https://nop-station.com</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Gravityer</t>
+          <t>NULogic</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>https://gravityer.com</t>
+          <t>https://nulogic.io</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1014,12 +1014,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>InStudio</t>
+          <t>88medias</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>https://instudio.digital</t>
+          <t>https://88medias.com</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1036,17 +1036,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Posibolt</t>
+          <t>Gravityer</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>https://posibolt.com</t>
+          <t>https://gravityer.com</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+          <t>Fashion Ecommerce Personalization &amp; Customer Experience Agencies</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1058,61 +1058,61 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Louis Innovations</t>
+          <t>InStudio</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>https://louis-innovations.com</t>
+          <t>https://instudio.digital</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Feed Management Specialists</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Raulji Technologies</t>
+          <t>Posibolt</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>https://rauljitechnologies.com</t>
+          <t>https://posibolt.com</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>intouch</t>
+          <t>Louis Innovations</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>https://intouchmena.com</t>
+          <t>https://louis-innovations.com</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce Product Feed Management Specialists</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>A101 (Atelier 101)</t>
+          <t>Raulji Technologies</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>https://a101.com</t>
+          <t>https://rauljitechnologies.com</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1139,41 +1139,41 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Krish TechnoLabs</t>
+          <t>intouch</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>https://krishtechnolabs.com</t>
+          <t>https://intouchmena.com</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Carmatec Qatar</t>
+          <t>A101 (Atelier 101)</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>https://carmatec.qa</t>
+          <t>https://a101.com</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1190,17 +1190,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Brainvire</t>
+          <t>Krish TechnoLabs</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>https://brainvire.com</t>
+          <t>https://krishtechnolabs.com</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1212,39 +1212,39 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>WAC (Webandcrafts)</t>
+          <t>Carmatec Qatar</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>https://webandcrafts.com</t>
+          <t>https://carmatec.qa</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>A2Z Media</t>
+          <t>Brainvire</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>https://a2z.media</t>
+          <t>https://brainvire.com</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1256,39 +1256,39 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>ABECODS</t>
+          <t>WAC (Webandcrafts)</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>https://abecods.com</t>
+          <t>https://webandcrafts.com</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>AGM Global Services</t>
+          <t>A2Z Media</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>https://agmglobal.co</t>
+          <t>https://a2z.media</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1300,78 +1300,78 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Xpert Solutions</t>
+          <t>ABECODS</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>https://xpertsolutions.qa</t>
+          <t>https://abecods.com</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>scandiweb</t>
+          <t>AGM Global Services</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>https://scandiweb.com</t>
+          <t>https://agmglobal.co</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Codilar</t>
+          <t>Xpert Solutions</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>https://codilar.com</t>
+          <t>https://xpertsolutions.qa</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Devsinc (formerly Alchemative)</t>
+          <t>scandiweb</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>https://devsinc.com</t>
+          <t>https://scandiweb.com</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1381,24 +1381,24 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Brainiac Studio</t>
+          <t>Codilar</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>https://brainiac.studio</t>
+          <t>https://codilar.com</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -1410,17 +1410,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Aegeantic (formerly FeatureMind)</t>
+          <t>Devsinc (formerly Alchemative)</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>https://aegeantic.com</t>
+          <t>https://devsinc.com</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -1432,105 +1432,105 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>iHorizons</t>
+          <t>Brainiac Studio</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>https://ihorizons.com</t>
+          <t>https://brainiac.studio</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Digiturnal</t>
+          <t>Aegeantic (formerly FeatureMind)</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>https://digiturnal.com</t>
+          <t>https://aegeantic.com</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Digital Marketing Agencies</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Persona AI</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Codes &amp; Colors</t>
+          <t>iHorizons</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>https://codesncolors.com</t>
+          <t>https://ihorizons.com</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>FirstDraftStudio</t>
+          <t>Digiturnal</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>https://firstdraftstudio.in</t>
+          <t>https://digiturnal.com</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Fashion Ecommerce Digital Marketing Agencies</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Persona AI</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>BIMO Group</t>
+          <t>Codes &amp; Colors</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>https://bimogroup.co</t>
+          <t>https://codesncolors.com</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -1542,83 +1542,83 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>DGTLbase</t>
+          <t>FirstDraftStudio</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>https://dgtlbase.com</t>
+          <t>https://firstdraftstudio.in</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>ControlF5</t>
+          <t>BIMO Group</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>https://controlf5.in</t>
+          <t>https://bimogroup.co</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce SEO Agencies &amp; Consultants</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Fundal Media</t>
+          <t>DGTLbase</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>https://fundalmedia.dk</t>
+          <t>https://dgtlbase.com</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Digital Marketing Agencies</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Persona AI</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Screen Pages</t>
+          <t>ControlF5</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>https://screenpages.com</t>
+          <t>https://controlf5.in</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce SEO Agencies &amp; Consultants</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -1630,27 +1630,71 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>Fundal Media</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>https://fundalmedia.dk</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Fashion Ecommerce Digital Marketing Agencies</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Persona AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Screen Pages</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>https://screenpages.com</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce Website Development Agencies</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Autommerce OS</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
           <t>Nurotex</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>https://nurotex.com</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>Ecommerce SEO Agencies &amp; Consultants</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Autommerce OS</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D55"/>
+  <autoFilter ref="A1:D57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/excel/Autommerce_Partners_Qatar.xlsx
+++ b/data/excel/Autommerce_Partners_Qatar.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partners" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Partners'!$A$1:$D$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Partners'!$A$1:$D$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1168,12 +1168,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>A101 (Atelier 101)</t>
+          <t>Sitemap Web Design Qatar</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>https://a101.com</t>
+          <t>https://sitemap.qa</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1183,24 +1183,24 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Krish TechnoLabs</t>
+          <t>Shafrah</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>https://krishtechnolabs.com</t>
+          <t>https://shafrah.qa</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1212,34 +1212,34 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Carmatec Qatar</t>
+          <t>Galaxium Coding</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>https://carmatec.qa</t>
+          <t>https://galaxiumcoding.com</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Brainvire</t>
+          <t>A101 (Atelier 101)</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>https://brainvire.com</t>
+          <t>https://a101.com</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1256,39 +1256,39 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>WAC (Webandcrafts)</t>
+          <t>Krish TechnoLabs</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>https://webandcrafts.com</t>
+          <t>https://krishtechnolabs.com</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>A2Z Media</t>
+          <t>Carmatec Qatar</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>https://a2z.media</t>
+          <t>https://carmatec.qa</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1300,17 +1300,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ABECODS</t>
+          <t>Brainvire</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>https://abecods.com</t>
+          <t>https://brainvire.com</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1322,83 +1322,83 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>AGM Global Services</t>
+          <t>WAC (Webandcrafts)</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>https://agmglobal.co</t>
+          <t>https://webandcrafts.com</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Xpert Solutions</t>
+          <t>A2Z Media</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>https://xpertsolutions.qa</t>
+          <t>https://a2z.media</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>scandiweb</t>
+          <t>ABECODS</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>https://scandiweb.com</t>
+          <t>https://abecods.com</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Codilar</t>
+          <t>AGM Global Services</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>https://codilar.com</t>
+          <t>https://agmglobal.co</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -1410,12 +1410,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Devsinc (formerly Alchemative)</t>
+          <t>Xpert Solutions</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>https://devsinc.com</t>
+          <t>https://xpertsolutions.qa</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -1425,19 +1425,19 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Brainiac Studio</t>
+          <t>scandiweb</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>https://brainiac.studio</t>
+          <t>https://scandiweb.com</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1447,19 +1447,19 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Aegeantic (formerly FeatureMind)</t>
+          <t>Codilar</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>https://aegeantic.com</t>
+          <t>https://codilar.com</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -1476,61 +1476,61 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>iHorizons</t>
+          <t>Devsinc (formerly Alchemative)</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>https://ihorizons.com</t>
+          <t>https://devsinc.com</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Digiturnal</t>
+          <t>Brainiac Studio</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>https://digiturnal.com</t>
+          <t>https://brainiac.studio</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Digital Marketing Agencies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Persona AI</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Codes &amp; Colors</t>
+          <t>Aegeantic (formerly FeatureMind)</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>https://codesncolors.com</t>
+          <t>https://aegeantic.com</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -1542,127 +1542,127 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>FirstDraftStudio</t>
+          <t>iHorizons</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>https://firstdraftstudio.in</t>
+          <t>https://ihorizons.com</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>BIMO Group</t>
+          <t>Digiturnal</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>https://bimogroup.co</t>
+          <t>https://digiturnal.com</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Fashion Ecommerce Digital Marketing Agencies</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Persona AI</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>DGTLbase</t>
+          <t>Codes &amp; Colors</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>https://dgtlbase.com</t>
+          <t>https://codesncolors.com</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>ControlF5</t>
+          <t>FirstDraftStudio</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>https://controlf5.in</t>
+          <t>https://firstdraftstudio.in</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce SEO Agencies &amp; Consultants</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Fundal Media</t>
+          <t>BIMO Group</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>https://fundalmedia.dk</t>
+          <t>https://bimogroup.co</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Digital Marketing Agencies</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Persona AI</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Screen Pages</t>
+          <t>DGTLbase</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>https://screenpages.com</t>
+          <t>https://dgtlbase.com</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -1674,27 +1674,93 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>ControlF5</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>https://controlf5.in</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce SEO Agencies &amp; Consultants</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Autommerce OS</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Fundal Media</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>https://fundalmedia.dk</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Fashion Ecommerce Digital Marketing Agencies</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Persona AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Screen Pages</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>https://screenpages.com</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce Website Development Agencies</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Autommerce OS</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
           <t>Nurotex</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>https://nurotex.com</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Ecommerce SEO Agencies &amp; Consultants</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Autommerce OS</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D57"/>
+  <autoFilter ref="A1:D60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/excel/Autommerce_Partners_Qatar.xlsx
+++ b/data/excel/Autommerce_Partners_Qatar.xlsx
@@ -7,10 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partners" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company details" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision makers" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Partners'!$A$1:$D$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Company details'!$A$1:$G$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decision makers'!$A$1:$G$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,8 +30,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,10 +68,10 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -427,19 +435,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="72" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Company Name</t>
@@ -458,6 +470,21 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Product Fit</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Emails</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
         </is>
       </c>
     </row>
@@ -482,6 +509,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -504,6 +534,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -526,6 +559,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -548,6 +584,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -570,6 +609,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -592,6 +634,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -614,6 +659,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -636,6 +684,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -658,6 +709,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -680,6 +734,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -702,6 +759,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -724,6 +784,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -746,6 +809,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -768,6 +834,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -790,6 +859,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -812,6 +884,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -834,6 +909,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -856,6 +934,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -878,6 +959,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -900,6 +984,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -922,6 +1009,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -944,6 +1034,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -966,6 +1059,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -988,6 +1084,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1010,6 +1109,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1032,6 +1134,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1054,6 +1159,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1076,6 +1184,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1098,6 +1209,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1120,6 +1234,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1142,6 +1259,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1164,6 +1284,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1186,6 +1309,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1208,6 +1334,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1230,6 +1359,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1252,6 +1384,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1274,6 +1409,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1296,6 +1434,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1318,6 +1459,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1340,6 +1484,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1362,6 +1509,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1384,6 +1534,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1406,6 +1559,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1428,6 +1584,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1450,6 +1609,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1472,6 +1634,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1494,6 +1659,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1516,6 +1684,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1538,6 +1709,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1560,6 +1734,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1582,6 +1759,9 @@
           <t>Persona AI</t>
         </is>
       </c>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1604,6 +1784,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1626,6 +1809,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1648,6 +1834,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -1670,6 +1859,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -1692,6 +1884,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1714,6 +1909,9 @@
           <t>Persona AI</t>
         </is>
       </c>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -1736,6 +1934,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -1758,9 +1959,76 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D60"/>
+  <autoFilter ref="A1:G60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F4E79"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>